--- a/output/2025_A04_SECCION_L_TABLAS.xlsx
+++ b/output/2025_A04_SECCION_L_TABLAS.xlsx
@@ -330,7 +330,7 @@
     <t>Centro de Salud Familiar Dra. Haydeé López Casoou</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Lo Chacón</t>
+    <t>CECOSF Wilma Yoli Gomez Conejera</t>
   </si>
   <si>
     <t>Centro de Salud Familiar El Monte</t>
